--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T08:58:38+00:00</t>
+    <t>2025-11-07T10:40:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T10:40:44+00:00</t>
+    <t>2025-11-25T08:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T08:22:04+00:00</t>
+    <t>2026-01-16T18:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T18:04:25+00:00</t>
+    <t>2026-01-23T16:54:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T16:54:57+00:00</t>
+    <t>2026-01-23T16:56:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T16:56:48+00:00</t>
+    <t>2026-02-09T09:37:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T09:37:19+00:00</t>
+    <t>2026-02-23T11:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,6 +125,12 @@
   </si>
   <si>
     <t>http://data.esante.gouv.fr/ansm/medicament/substance</t>
+  </si>
+  <si>
+    <t>http://data.esante.gouv.fr/ansm/medicament/Presentation</t>
+  </si>
+  <si>
+    <t>http://data.esante.gouv.fr/ansm/medicament/SpecialitePharmaceutique</t>
   </si>
 </sst>
 </file>
@@ -510,4 +518,84 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T11:15:05+00:00</t>
+    <t>2026-04-02T15:16:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:16:30+00:00</t>
+    <t>2026-05-04T12:24:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:24:40+00:00</t>
+    <t>2026-05-04T13:30:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:30:13+00:00</t>
+    <t>2026-05-06T13:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T13:16:54+00:00</t>
+    <t>2026-05-10T16:39:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-10T16:39:38+00:00</t>
+    <t>2026-05-10T16:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-10T16:47:08+00:00</t>
+    <t>2026-05-11T06:03:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T06:03:48+00:00</t>
+    <t>2026-05-11T06:11:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-medication-code.xlsx
+++ b/main/ig/ValueSet-fr-medication-code.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T06:11:37+00:00</t>
+    <t>2026-07-10T14:23:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
